--- a/outputs/fifa_team_statistics/excel_por_categoria/Goalkeeping.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Goalkeeping.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -908,27 +908,27 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E16" t="n">
         <v>2</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G16" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -938,27 +938,27 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G17" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -968,27 +968,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Curaçao</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="H18" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -998,27 +998,27 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G19" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -1028,27 +1028,27 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IR Iran</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -1058,27 +1058,27 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G21" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1088,27 +1088,27 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="H22" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -1118,27 +1118,27 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="G23" t="n">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1148,27 +1148,27 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="G24" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -1178,24 +1178,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G25" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="H25" t="n">
         <v>9</v>
@@ -1208,27 +1208,27 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G26" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="H26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -1238,11 +1238,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1252,13 +1252,13 @@
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="G27" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -1336,16 +1336,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="G30" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H30" t="n">
         <v>8</v>
@@ -1998,10 +1998,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>16.9375</v>
+        <v>16.91666666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>10.39723009349227</v>
+        <v>10.55851644425229</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -2010,7 +2010,7 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
         <v>27</v>
@@ -2029,10 +2029,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>4.875</v>
+        <v>5.020833333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>3.070969075687638</v>
+        <v>3.124982269453247</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -2044,7 +2044,7 @@
         <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="I3" t="n">
         <v>12</v>
@@ -2060,10 +2060,10 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9944437840905397</v>
+        <v>1.007067225741718</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2091,22 +2091,22 @@
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>64.8125</v>
+        <v>66.9375</v>
       </c>
       <c r="D5" t="n">
-        <v>20.61156074076422</v>
+        <v>20.71530038915115</v>
       </c>
       <c r="E5" t="n">
         <v>31</v>
       </c>
       <c r="F5" t="n">
-        <v>50.5</v>
+        <v>52.5</v>
       </c>
       <c r="G5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H5" t="n">
-        <v>77.25</v>
+        <v>81.25</v>
       </c>
       <c r="I5" t="n">
         <v>124</v>
@@ -2122,22 +2122,22 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>54.72916666666666</v>
+        <v>56.45833333333334</v>
       </c>
       <c r="D6" t="n">
-        <v>17.88228599710533</v>
+        <v>17.63815778161308</v>
       </c>
       <c r="E6" t="n">
         <v>26</v>
       </c>
       <c r="F6" t="n">
-        <v>41.75</v>
+        <v>43.75</v>
       </c>
       <c r="G6" t="n">
-        <v>54</v>
+        <v>55.5</v>
       </c>
       <c r="H6" t="n">
-        <v>65</v>
+        <v>66.5</v>
       </c>
       <c r="I6" t="n">
         <v>103</v>
@@ -2153,10 +2153,10 @@
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>10.27083333333333</v>
+        <v>10.52083333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>4.518235314213939</v>
+        <v>4.419442457053341</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -2165,10 +2165,10 @@
         <v>7.75</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="I7" t="n">
         <v>24</v>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Goalkeeping.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Goalkeeping.xlsx
@@ -426,56 +426,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Goals Conceded</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Clean Sheets</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Goals Conceded</t>
+          <t>Goalkeeper Actions Inside the Penalty Area</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Clean Sheets</t>
+          <t>Goalkeeper Actions Outside the Penalty Area</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Goalkeeper Actions Inside the Penalty Area</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Goalkeeper Actions Outside the Penalty Area</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Goalkeeper Saves</t>
         </is>
@@ -484,1440 +472,1056 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
-      </c>
-      <c r="G2" t="n">
-        <v>41</v>
-      </c>
-      <c r="H2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
-      </c>
-      <c r="G3" t="n">
-        <v>31</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
-      </c>
-      <c r="G4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
-      </c>
-      <c r="G5" t="n">
-        <v>56</v>
-      </c>
-      <c r="H5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>54</v>
-      </c>
-      <c r="G6" t="n">
-        <v>47</v>
-      </c>
-      <c r="H6" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cabo Verde</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>96</v>
-      </c>
-      <c r="G7" t="n">
-        <v>71</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
-      </c>
-      <c r="G8" t="n">
-        <v>34</v>
-      </c>
-      <c r="H8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
-        <v>37</v>
-      </c>
-      <c r="G9" t="n">
-        <v>36</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>3</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
+      <c r="C10" t="n">
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="F10" t="n">
-        <v>84</v>
-      </c>
-      <c r="G10" t="n">
-        <v>68</v>
-      </c>
-      <c r="H10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
-      </c>
-      <c r="G11" t="n">
-        <v>43</v>
-      </c>
-      <c r="H11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>83</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
-      </c>
-      <c r="G12" t="n">
-        <v>36</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
-      </c>
-      <c r="G13" t="n">
-        <v>55</v>
-      </c>
-      <c r="H13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="F14" t="n">
-        <v>116</v>
-      </c>
-      <c r="G14" t="n">
-        <v>103</v>
-      </c>
-      <c r="H14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
-      </c>
-      <c r="G15" t="n">
-        <v>54</v>
-      </c>
-      <c r="H15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
-      </c>
-      <c r="G16" t="n">
-        <v>47</v>
-      </c>
-      <c r="H16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F17" t="n">
-        <v>79</v>
-      </c>
-      <c r="G17" t="n">
-        <v>65</v>
-      </c>
-      <c r="H17" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
-      </c>
-      <c r="G18" t="n">
-        <v>48</v>
-      </c>
-      <c r="H18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F19" t="n">
-        <v>81</v>
-      </c>
-      <c r="G19" t="n">
-        <v>72</v>
-      </c>
-      <c r="H19" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>16</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
       </c>
       <c r="D20" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F20" t="n">
-        <v>68</v>
-      </c>
-      <c r="G20" t="n">
-        <v>63</v>
-      </c>
-      <c r="H20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>IR Iran</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F21" t="n">
-        <v>75</v>
-      </c>
-      <c r="G21" t="n">
-        <v>65</v>
-      </c>
-      <c r="H21" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F22" t="n">
-        <v>78</v>
-      </c>
-      <c r="G22" t="n">
-        <v>64</v>
-      </c>
-      <c r="H22" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="F23" t="n">
-        <v>59</v>
-      </c>
-      <c r="G23" t="n">
-        <v>49</v>
-      </c>
-      <c r="H23" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>16</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
-        <v>86</v>
-      </c>
-      <c r="G24" t="n">
-        <v>78</v>
-      </c>
-      <c r="H24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>16</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Scotland</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>81</v>
       </c>
       <c r="F25" t="n">
-        <v>75</v>
-      </c>
-      <c r="G25" t="n">
-        <v>64</v>
-      </c>
-      <c r="H25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>16</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="F26" t="n">
-        <v>87</v>
-      </c>
-      <c r="G26" t="n">
-        <v>70</v>
-      </c>
-      <c r="H26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="F27" t="n">
-        <v>72</v>
-      </c>
-      <c r="G27" t="n">
-        <v>59</v>
-      </c>
-      <c r="H27" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F28" t="n">
-        <v>36</v>
-      </c>
-      <c r="G28" t="n">
-        <v>33</v>
-      </c>
-      <c r="H28" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
       </c>
       <c r="D29" t="n">
+        <v>51</v>
+      </c>
+      <c r="E29" t="n">
+        <v>41</v>
+      </c>
+      <c r="F29" t="n">
         <v>6</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>49</v>
-      </c>
-      <c r="G29" t="n">
-        <v>44</v>
-      </c>
-      <c r="H29" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
-        <v>92</v>
-      </c>
-      <c r="G30" t="n">
-        <v>70</v>
-      </c>
-      <c r="H30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Congo DR</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F31" t="n">
-        <v>83</v>
-      </c>
-      <c r="G31" t="n">
-        <v>70</v>
-      </c>
-      <c r="H31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F32" t="n">
-        <v>60</v>
-      </c>
-      <c r="G32" t="n">
-        <v>52</v>
-      </c>
-      <c r="H32" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F33" t="n">
-        <v>64</v>
-      </c>
-      <c r="G33" t="n">
-        <v>56</v>
-      </c>
-      <c r="H33" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F34" t="n">
-        <v>61</v>
-      </c>
-      <c r="G34" t="n">
-        <v>45</v>
-      </c>
-      <c r="H34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="F35" t="n">
-        <v>56</v>
-      </c>
-      <c r="G35" t="n">
-        <v>48</v>
-      </c>
-      <c r="H35" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F36" t="n">
-        <v>94</v>
-      </c>
-      <c r="G36" t="n">
-        <v>81</v>
-      </c>
-      <c r="H36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="F37" t="n">
-        <v>70</v>
-      </c>
-      <c r="G37" t="n">
-        <v>56</v>
-      </c>
-      <c r="H37" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Korea Republic</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="F38" t="n">
-        <v>42</v>
-      </c>
-      <c r="G38" t="n">
-        <v>34</v>
-      </c>
-      <c r="H38" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F39" t="n">
-        <v>57</v>
-      </c>
-      <c r="G39" t="n">
-        <v>54</v>
-      </c>
-      <c r="H39" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>27</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F40" t="n">
-        <v>97</v>
-      </c>
-      <c r="G40" t="n">
-        <v>88</v>
-      </c>
-      <c r="H40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F41" t="n">
-        <v>85</v>
-      </c>
-      <c r="G41" t="n">
-        <v>75</v>
-      </c>
-      <c r="H41" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F42" t="n">
-        <v>48</v>
-      </c>
-      <c r="G42" t="n">
-        <v>42</v>
-      </c>
-      <c r="H42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>27</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
+        <v>10</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F43" t="n">
-        <v>124</v>
-      </c>
-      <c r="G43" t="n">
-        <v>103</v>
-      </c>
-      <c r="H43" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F44" t="n">
-        <v>76</v>
-      </c>
-      <c r="G44" t="n">
-        <v>66</v>
-      </c>
-      <c r="H44" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F45" t="n">
-        <v>38</v>
-      </c>
-      <c r="G45" t="n">
-        <v>34</v>
-      </c>
-      <c r="H45" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F46" t="n">
-        <v>77</v>
-      </c>
-      <c r="G46" t="n">
-        <v>64</v>
-      </c>
-      <c r="H46" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C47" t="n">
+        <v>2</v>
       </c>
       <c r="D47" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F47" t="n">
-        <v>55</v>
-      </c>
-      <c r="G47" t="n">
-        <v>46</v>
-      </c>
-      <c r="H47" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>27</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F48" t="n">
-        <v>48</v>
-      </c>
-      <c r="G48" t="n">
-        <v>39</v>
-      </c>
-      <c r="H48" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Goalkeeping</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>27</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="F49" t="n">
-        <v>82</v>
-      </c>
-      <c r="G49" t="n">
-        <v>65</v>
-      </c>
-      <c r="H49" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1932,7 +1536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1991,186 +1595,155 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Goals Conceded</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>16.91666666666667</v>
+        <v>5.020833333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>10.55851644425229</v>
+        <v>3.124982269453247</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>27</v>
+        <v>7.25</v>
       </c>
       <c r="I2" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Goals Conceded</t>
+          <t>Clean Sheets</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>5.020833333333333</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>3.124982269453247</v>
+        <v>1.007067225741718</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>4</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="I3" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Clean Sheets</t>
+          <t>Goalkeeper Actions Inside the Penalty Area</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9166666666666666</v>
+        <v>66.9375</v>
       </c>
       <c r="D4" t="n">
-        <v>1.007067225741718</v>
+        <v>20.71530038915115</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>52.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>81.25</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Goalkeeper Actions Inside the Penalty Area</t>
+          <t>Goalkeeper Actions Outside the Penalty Area</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>66.9375</v>
+        <v>56.45833333333334</v>
       </c>
       <c r="D5" t="n">
-        <v>20.71530038915115</v>
+        <v>17.63815778161308</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>52.5</v>
+        <v>43.75</v>
       </c>
       <c r="G5" t="n">
-        <v>64</v>
+        <v>55.5</v>
       </c>
       <c r="H5" t="n">
-        <v>81.25</v>
+        <v>66.5</v>
       </c>
       <c r="I5" t="n">
-        <v>124</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Goalkeeper Actions Outside the Penalty Area</t>
+          <t>Goalkeeper Saves</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>56.45833333333334</v>
+        <v>10.52083333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>17.63815778161308</v>
+        <v>4.419442457053341</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>43.75</v>
+        <v>7.75</v>
       </c>
       <c r="G6" t="n">
-        <v>55.5</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>66.5</v>
+        <v>12.25</v>
       </c>
       <c r="I6" t="n">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Goalkeeper Saves</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>48</v>
-      </c>
-      <c r="C7" t="n">
-        <v>10.52083333333333</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.419442457053341</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="G7" t="n">
-        <v>10</v>
-      </c>
-      <c r="H7" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="I7" t="n">
         <v>24</v>
       </c>
     </row>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Goalkeeping.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Goalkeeping.xlsx
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -554,7 +554,7 @@
         <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
         <v>43</v>
@@ -1602,10 +1602,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>5.020833333333333</v>
+        <v>5.083333333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>3.124982269453247</v>
+        <v>3.174588821311693</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
         <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>12</v>
@@ -1633,10 +1633,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9375</v>
       </c>
       <c r="D3" t="n">
-        <v>1.007067225741718</v>
+        <v>1.060033118711844</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1726,10 +1726,10 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>10.52083333333333</v>
+        <v>10.5625</v>
       </c>
       <c r="D6" t="n">
-        <v>4.419442457053341</v>
+        <v>4.404573300269483</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
